--- a/site/exports/csu-humanities.xlsx
+++ b/site/exports/csu-humanities.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -452,9 +452,9 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,119 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>人文学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>当前任职未经独立人事核验，全部现任导航false。；无本人导师事实，不把博士生导师职务当作本人导师关系。；仅职业必要摘录，非完整HTTP原件；搜索时间只留实际对话时钟区间，页面读取时刻逐次真实记录。；官网有年份作品但没有逐项作者署名，本轮0正式书目且不外查论文；不代表没有成果。；目录标题为人文学院，但过滤器仍显示文学与新闻传播学院；不在本轮推法律更名或行政父节点。；学士、硕士为标签，degree_awarded=null；博士有明确取得学位句，授位年/月/日未知。；博士学习栏目1999.3—2003.6与叙述留学1999年3月—2004年8月原样保留，未强行对齐。；工作栏目中南开始2004-7与页头入职2004-08-25不同，未决定哪一个正确。；工作栏目中南区间终点2019-6与在职标签并存，未据此确认当前或离职；国家民委与民族出版社标签不拆为两个雇主。；具体系别未知，不用中国现当代文学研究方向推中文系成员身份。；来源差异/限制：目录标题人文学院与页面筛选或任职记录的文学与新闻传播学院标签分别保留，不推断法律更名、行政重组或当前人事。；来源差异/限制：教育栏目博士学习1999-03至2003-06与叙述留学1999-03至2004-08分别保留，不据终点推授位时间。；来源差异/限制：任职栏目2004-07与页头入职2004-08-25并存，保留原值；2019-06终点与在职标签不用于认定离职或当前在岗。；来源记载职业信息：来源职业身份与角色：指导他人的资格：博士生导师；资格标签：归国博士；来源说明：资格标签不新增授位机构或授位日期；二级教授已有结构。。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>吴宝林</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>人文学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>当前任职未经独立人事核验，全部现任导航false。；无本人导师事实，不把博士生导师职务当作本人导师关系。；仅职业必要摘录，非完整HTTP原件；搜索时间只留实际对话时钟区间，页面读取时刻逐次真实记录。；官网有年份作品但没有逐项作者署名，本轮0正式书目且不外查论文；不代表没有成果。；目录标题为人文学院，但过滤器仍显示文学与新闻传播学院；不在本轮推法律更名或行政父节点。；两个武汉大学学位明确获得，但专业与阶段映射、起止日期和具体授位时间未知。；北京大学博士毕业不等于已验证博士学位授予，degree_awarded=null。；中文系归属来自个人职业表述；独立目录为全院列名，未给个人逐系分类。；来源差异/限制：目录标题人文学院与页面筛选或任职记录的文学与新闻传播学院标签分别保留，不推断法律更名、行政重组或当前人事。；来源记载职业信息：合述教育语境：机构与专业原述：武汉大学：测绘工程、汉语言文学及中国现当代文学；北京大学中文系博士毕业。；阶段与专业的逐项对应未核实；来源说明：保留专业序列，不构造一个未被明确说明的单独测绘学位或非学位事件。。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。；来源记载职业信息：来源职业身份与角色：指导他人的资格：博士生导师。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：鲁迅研究；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；教学时间语境：官网列示课程，不确认当前开课；目的性摘取3门非完整课程表。；来源ID：new-recovery-csu-wubaolin-s001-5416ae66a855；https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm | 现代文学研究专题；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；教学时间语境：官网列示课程，不确认当前开课；目的性摘取3门非完整课程表。；来源ID：new-recovery-csu-wubaolin-s001-5416ae66a855；https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm | 中国现代文学史；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；教学时间语境：官网列示课程，不确认当前开课；目的性摘取3门非完整课程表。；来源ID：new-recovery-csu-wubaolin-s001-5416ae66a855；https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,13 +746,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="25.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -720,7 +828,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1149,8 +1257,681 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>education_label</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>学士学位</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1987-07</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1991-05</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>汉语言文学</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>来源为教育经历条目的学位标签，未见明确获授该学位句，故degree_awarded=null，不推为false。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：学士</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>education_label</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>硕士学位</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>湘潭大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1991-09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1994-06</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>古代文学</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>来源为教育经历条目的学位标签，未见明确获授该学位句，故degree_awarded=null，不推为false。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：硕士</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>博士学位</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>新西兰怀卡托大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1999-03</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2003-06</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>文化传播学</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>教育栏目给出1999.3—2003.6；简介另写1999年3月至2004年8月出国留学并取得博士学位。学习期与留学期不同字段，不强行统一、不以终年填授位年。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>编辑、记者</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>湖南日报</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1994-06</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1999-06</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>编辑</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>国家民委与民族出版社</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2003-09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2004-06</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>中南大学文学与新闻传播学院</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2004-07</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>保留工作栏目列出的区间和“在职”标签，不由区间断言2019离职。与页头入职时间2004-08-25不同，不自行修正。；任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>二级教授</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>吴宝林</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>文学学士</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>武汉大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>简介联合陈述武汉大学求学并获学士、硕士；未将测绘工程、汉语言文学、中国现当代文学三个专业强配到两个学位阶段，具体日期及法律授位实体未知。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：学士</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>吴宝林</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>硕士学位</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>武汉大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>简介联合陈述武汉大学求学并获学士、硕士；未将测绘工程、汉语言文学、中国现当代文学三个专业强配到两个学位阶段，具体日期及法律授位实体未知。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：硕士</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>吴宝林</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>education_label</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>博士毕业</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>博士毕业是学历完成表述，未见明确博士学位授予句；独立学位标签亦不能替代授予证据，故null。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士；来源department：中文系</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>吴宝林</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>副教授；中文系副系主任</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>中南大学人文学院</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1158,6 +1939,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1589,14 +2381,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16.8" customWidth="1" min="2" max="2"/>
+    <col width="60.2" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1704,11 +2496,163 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-csu-niemao-s001-be19ebbb37b6</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/niemao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T23:21:45.856Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>聂茂</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-csu-niemao-s002-97cd192981f4</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://clj.csu.edu.cn/xygk/szdw.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T23:21:57.662Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>吴宝林</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-csu-wubaolin-s001-5416ae66a855</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://faculty.csu.edu.cn/wubaolin/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T23:21:45.301Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>吴宝林</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-csu-wubaolin-s002-97cd192981f4</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://clj.csu.edu.cn/xygk/szdw.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T23:21:57.662Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>csu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>中南大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/csu-humanities.xlsx
+++ b/site/exports/csu-humanities.xlsx
@@ -1298,7 +1298,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L15" s="2" t="b">
@@ -1790,7 +1790,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L16" s="2" t="b">
@@ -1849,7 +1849,7 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
